--- a/doc/QTL - Task Tracker (June 2026).xlsx
+++ b/doc/QTL - Task Tracker (June 2026).xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$F$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$F$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,6 +87,9 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -141,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -177,6 +181,19 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -598,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6341,8 +6358,578 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>Fuel and grease counted on Oil detail</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>Every oil change also burns diesel treatment and grease - roughly $6 to $10 a job - and the page ignored both. Oil detail now shows Fuel and Grease from the package linked to that engine, so Profit is the real number.</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="n">
+        <v>46261</v>
+      </c>
+      <c r="F192" s="19" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>Oil groups - one base price per family of grades</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>Every oil line on a job was charged at one base price, so a synthetic 5W30 costing $8.30/L was quoted at the 15W40 rate of $5.02/L and staff corrected it by hand. Each family of grades now has its own base price, with separate bulk and gallon rates, under Settings &gt; Pricing &gt; Oil groups.</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F193" s="19" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Group rates seeded from what the shop bills</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>The three well-used groups start at the price actually charged on the last 1,000 oil lines - 15W40 $5.37/L, 10W30 $6.05/L, 5W30 synthetic $9.34/L. Gear &amp; Trans and every gallon rate are left blank on purpose, so those lines behave exactly as before until you set them.</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F194" s="20" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Oil types list shows the group and the charged rate</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>The oil grades list showed only a Base tick. It now shows which group prices each grade and the rate a job line will start at, so you can see what will be quoted without opening the group.</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F195" s="20" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Pricing &amp; Catalogue</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Catalogue codes accept dashes</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>Codes with a dash ('FF5588-NN') were rejected when saving an oil type or a service cost - only letters, digits and underscores were allowed. Dashes and lower case are now accepted, and the code is upper-cased on save.</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F196" s="21" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>Fuel and grease on Oil-change detailed pricing</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>The detailed page had no Fuel column, and its Grease column read a shop-wide cost row that does not exist, so it was blank for all 69 engines. Both now come from the engine's package. An amber dash means no package is linked, so the usage is unknown rather than zero.</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F197" s="21" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>Link engines to their labour package in one pass</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>Only 27 of 69 engines matched a package by name; the rest had to be linked one at a time. Engine types now proposes a package for each - matched on family, filter brand and model - and applies the ones you accept together. 28 were linked this way; the 14 it cannot call are listed with the packages that fitted.</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F198" s="19" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>Fixed sell prices editable on a part</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>Parts prices would not update: 103 parts carry a fixed price from the May 2026 sheet, and a fixed price beats the cost and margin calculation. The part now has a Fixed sell prices box showing the calculated price behind each tier, a warning when one is held, and a Clear button.</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F199" s="21" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>Fixed prices flagged on the All-filter price list</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>A price held at a fixed price is shown with a dotted underline, with a note on where to clear it, so it is obvious why it ignores edits to cost and margin.</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F200" s="20" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Payroll stays editable after approval</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>Entries, daily cash and payments froze the moment a week was approved or paid, so a wrong hour count found after payday could never be corrected. Everything stays editable at any status now, for the same people who could edit the draft, and every change is logged.</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F201" s="20" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>Delete payroll rows and weeks</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>An entry on the wrong employee, a duplicate cash day, a payment that never went out, or a week opened on the wrong date can now be removed. Each delete asks first and says what goes with it; deleting a week takes its entries and payments too.</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F202" s="19" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>Pay week details editable</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>A week booked on the wrong date or against the wrong shop had to be abandoned. Its dates, shop and notes can now be corrected in place.</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F203" s="20" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>EI, CPP, tax, vacation and WSIB switchable per person</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>Deductions applied to everyone unconditionally. Each is now a switch on the employee and on the pay entry - for family members who are EI-exempt, staff under 18 or over 70, and anyone off the shop's WSIB. Turning one off drops the employer side with it, and what is off is listed on the stub.</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F204" s="19" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>Holiday pay entered as hours and rate</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>Statutory holiday pay was typed in as a dollar amount. It is now hours times a rate, like regular and overtime, with the amount worked out for you. Leave the rate at 0 to use the regular one. Existing entries were split back into hours and rate and show the same dollars.</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F205" s="20" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>Printable payroll register, pay stubs and CSV</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>Print on a pay week gives the whole week as a register to sign and file, or one pay statement per employee, page-broken to hand out. The same data exports as CSV, the pay-week list exports too, and staff can print their own My Pay history. Hidden columns stay hidden on paper.</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="n">
+        <v>46265</v>
+      </c>
+      <c r="F206" s="19" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>Renaming an oil grade changes it everywhere</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>Oil grades were labelled from a fixed list that overrode Settings, so renaming a grade changed the settings table and nothing else - job lines, pickers, the grid and the print list kept the old name. The name in Settings &gt; Oil types is now the only source. Saved jobs keep the name they were saved with.</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F207" s="21" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>Gross column includes holiday pay</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>On a pay week the Gross column left holiday pay out while the Gross box above it, the printed register, the export and My Pay all counted it, so the column never matched the total. It is included everywhere now.</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F208" s="21" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>Link packages button only shows when it can help</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>The button offered to link packages even when every remaining engine needed a human decision. It now appears only when there is something to apply; the rest are set in the Labour package column.</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F209" s="20" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>Engine types page loads in one wait</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>The page fetched its package suggestions in a second trip after everything else had loaded. They are fetched alongside the rest now.</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F210" s="20" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F191"/>
+  <autoFilter ref="A1:F210"/>
   <conditionalFormatting sqref="A2:E191">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F2="Feature"</formula>
@@ -6375,7 +6962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6395,10 +6982,11 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>190 tasks · 2026-05-30 to 2026-08-20</t>
-        </is>
-      </c>
-    </row>
+          <t>209 tasks · 2026-05-30 to 2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -6412,8 +7000,8 @@
           <t>Feature</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
-        <v>68</v>
+      <c r="B5" s="22" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -6422,8 +7010,8 @@
           <t>Change</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>82</v>
+      <c r="B6" s="22" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -6432,10 +7020,11 @@
           <t>Bug</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
+      <c r="B7" s="22" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
@@ -6471,18 +7060,18 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="23" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -6490,18 +7079,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="23" t="n">
         <v>13</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -6509,18 +7098,18 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="23" t="n">
         <v>15</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -6528,168 +7117,191 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="B14" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>By area</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>Sales &amp; Jobs</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Parts &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>Customer &amp; Vehicle</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>Vendors &amp; Expenses</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Oil Grid &amp; Pricing</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>Roles &amp; Permissions</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="E14" s="18" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>By area</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sales &amp; Jobs</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Parts &amp; Pricing</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Customer &amp; Vehicle</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Vendors &amp; Expenses</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Roles &amp; Permissions</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Oil Grid &amp; Pricing</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>Packages</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
+      <c r="B26" s="22" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>UI &amp; Navigation</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
+      <c r="B27" s="22" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B28" s="22" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Pricing &amp; Catalogue</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="B29" s="22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="B30" s="22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>Dashboard &amp; Analytics</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B31" s="22" t="n">
         <v>3</v>
       </c>
     </row>
